--- a/selenium-tests/PrepWiseAI_Selenium_Test_Cases.xlsx
+++ b/selenium-tests/PrepWiseAI_Selenium_Test_Cases.xlsx
@@ -306,7 +306,7 @@
     <t>Smoke</t>
   </si>
   <si>
-    <t>Ready</t>
+    <t>Passed</t>
   </si>
   <si>
     <t>Automated</t>
